--- a/corr_matrix/residual_exam4A_1PL.xlsx
+++ b/corr_matrix/residual_exam4A_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>4A02</t>
@@ -565,76 +570,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08612448135393884</v>
+        <v>0.06142932322582859</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08491460848865381</v>
+        <v>-0.07505803114668086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0733737654050393</v>
+        <v>0.07788776548615284</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1054610870414173</v>
+        <v>-0.1164803823855678</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1787308929951696</v>
+        <v>0.1675110270959056</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03033563233419542</v>
+        <v>-0.0001358103482865656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03633878225065681</v>
+        <v>0.08430410904746641</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02022527151277422</v>
+        <v>-0.06518197803385899</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.03156057349854907</v>
+        <v>-0.05910174083749125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.115036642148845</v>
+        <v>0.1108574280871432</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.005320585099990513</v>
+        <v>-0.01005472373352051</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0309895504798232</v>
+        <v>-0.02919866317812313</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.010167815924502</v>
+        <v>-0.01652110070473159</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06274862662996503</v>
+        <v>-0.01574758136923303</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2879778325182079</v>
+        <v>-0.2664423905590795</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1005307437854741</v>
+        <v>-0.09676370678408867</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0234246176892712</v>
+        <v>-0.01344808262040014</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.289937324764146</v>
+        <v>-0.2891011301594047</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.129467551742682</v>
+        <v>-0.1389372538354036</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1274996302614811</v>
+        <v>-0.1058206984785341</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1266513046877031</v>
+        <v>-0.113435125818089</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05038743634038696</v>
+        <v>-0.04131472822192009</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2563450530171666</v>
+        <v>-0.2314271358869424</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.0606583256478611</v>
+        <v>-0.1045080928838213</v>
       </c>
     </row>
     <row r="3">
@@ -644,79 +649,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08612448135393884</v>
+        <v>0.06142932322582859</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1000754665976501</v>
+        <v>-0.1054399628312214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01511231224066872</v>
+        <v>0.008389853352905253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02288465058960031</v>
+        <v>0.01272393099029997</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05775782504354918</v>
+        <v>0.02479009911600766</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2300070610920869</v>
+        <v>-0.2088423892759686</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03262465548527024</v>
+        <v>-0.01231536790245246</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1904304170486608</v>
+        <v>0.1311458572529243</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.02486164170619122</v>
+        <v>-0.06168451493187681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01908623476245801</v>
+        <v>-0.001225231000302629</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04464396500874263</v>
+        <v>-0.08554976741476467</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1559109496315521</v>
+        <v>-0.1754706779003215</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.09802811676286918</v>
+        <v>-0.1282986512996324</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.02910423308593498</v>
+        <v>0.005390803511098182</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.07454092395583817</v>
+        <v>-0.09046689855553329</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.004314750711063078</v>
+        <v>-0.009155430853510173</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2537531499669427</v>
+        <v>0.09460719304213316</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09281486384247901</v>
+        <v>-0.1086641601778888</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.05628711763244174</v>
+        <v>-0.08680389514627654</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.132083829042015</v>
+        <v>-0.124628603062419</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.06565800076881249</v>
+        <v>-0.07563312811489989</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.07812496384373757</v>
+        <v>-0.09856726194527057</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1633930710272654</v>
+        <v>-0.1535980470188925</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.07889468769940283</v>
+        <v>-0.1687688053973208</v>
       </c>
     </row>
     <row r="4">
@@ -726,79 +731,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.08491460848865381</v>
+        <v>-0.07505803114668086</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1000754665976501</v>
+        <v>-0.1054399628312214</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.12697605598151</v>
+        <v>-0.1244973903516573</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09416573604462844</v>
+        <v>-0.1066721947274203</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.05908823499400193</v>
+        <v>-0.07081942824364267</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02543654199304072</v>
+        <v>0.004414366045008406</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08405945991302961</v>
+        <v>-0.03097934832898148</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2121035441269691</v>
+        <v>-0.2389597492136833</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.04308140878928639</v>
+        <v>-0.0694836871769368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1254533554195611</v>
+        <v>0.1184643473616116</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04508875124098461</v>
+        <v>-0.038391570805827</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1418409488252334</v>
+        <v>-0.1397984830157049</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1516497698866561</v>
+        <v>0.1494580070051232</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0132706050165777</v>
+        <v>0.06099766292635559</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1698049892625425</v>
+        <v>-0.1373443152881657</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3458779028144075</v>
+        <v>-0.3198448449012241</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003225457788512108</v>
+        <v>-0.0322294158618792</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09230591122672942</v>
+        <v>0.09904536120018702</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1371483270164527</v>
+        <v>-0.1453779068901319</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3128475457854189</v>
+        <v>-0.2793977700291272</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1378498937458855</v>
+        <v>0.1500949403203038</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08846006394704242</v>
+        <v>0.1031424048696561</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1558624613615861</v>
+        <v>0.1784076397552233</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05260816573364549</v>
+        <v>-0.1216951930520787</v>
       </c>
     </row>
     <row r="5">
@@ -808,79 +813,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0733737654050393</v>
+        <v>0.07788776548615284</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01511231224066872</v>
+        <v>0.008389853352905253</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.12697605598151</v>
+        <v>-0.1244973903516573</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3646419075600446</v>
+        <v>0.3419831022464119</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1985780678161243</v>
+        <v>-0.2038366639684794</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04405427721174383</v>
+        <v>0.04850253546098757</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3299542935597286</v>
+        <v>0.3358321108389308</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1708340394968761</v>
+        <v>-0.1862569580259524</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2127664205607351</v>
+        <v>0.2030837249025649</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03911441079194861</v>
+        <v>0.0291518275489075</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03917383475926822</v>
+        <v>0.04406701542697509</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08402179519841492</v>
+        <v>-0.09159127843255042</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1413832192368523</v>
+        <v>0.1295906476988291</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.08743853822678514</v>
+        <v>-0.08276809575200085</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02403164704658321</v>
+        <v>0.02757130748056327</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05349517525767633</v>
+        <v>0.05056421195681789</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1117365121049816</v>
+        <v>-0.1499544726593419</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1796645355347489</v>
+        <v>0.1654187283937949</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1279556361747688</v>
+        <v>-0.1432502264771037</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1331544537086789</v>
+        <v>-0.1346600688148256</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3578306650804607</v>
+        <v>-0.3612821256797281</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06291715035495396</v>
+        <v>0.06156912859658701</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1064287269247117</v>
+        <v>-0.1066983155019261</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1141399123091065</v>
+        <v>0.004023742310054235</v>
       </c>
     </row>
     <row r="6">
@@ -890,79 +895,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1054610870414173</v>
+        <v>-0.1164803823855678</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02288465058960031</v>
+        <v>0.01272393099029997</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09416573604462844</v>
+        <v>-0.1066721947274203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3646419075600446</v>
+        <v>0.3419831022464119</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1354604238562144</v>
+        <v>-0.167215442264363</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2079993296777172</v>
+        <v>-0.2368021079375125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01241562626470104</v>
+        <v>-0.005140770363835848</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1564434015163391</v>
+        <v>-0.1768402493286133</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01055909847799311</v>
+        <v>-0.02812539956889237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1053724602209355</v>
+        <v>0.06830064509733623</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1617247728694708</v>
+        <v>-0.1771628291451114</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.008624186383075961</v>
+        <v>-0.04766298966051171</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1823367016379244</v>
+        <v>0.1522367335188125</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2330217345192515</v>
+        <v>0.2110941022081083</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.05473024321424005</v>
+        <v>0.04313992752110613</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06478772439648009</v>
+        <v>0.05611819213621655</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2920659258482997</v>
+        <v>0.07877893377184686</v>
       </c>
       <c r="T6" t="n">
-        <v>0.229016999092037</v>
+        <v>0.1932548170751102</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.04960427331085888</v>
+        <v>-0.09703677862553618</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.08707703895241654</v>
+        <v>-0.1093541868981749</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.007962815931592107</v>
+        <v>-0.03863046187765157</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09823339310329221</v>
+        <v>0.07997241276484114</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.04878234568183844</v>
+        <v>-0.07470765839608567</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.07569129305361902</v>
+        <v>0.004721469054563258</v>
       </c>
     </row>
     <row r="7">
@@ -972,79 +977,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1787308929951696</v>
+        <v>0.1675110270959056</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05775782504354918</v>
+        <v>0.02479009911600766</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05908823499400193</v>
+        <v>-0.07081942824364267</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1985780678161243</v>
+        <v>-0.2038366639684794</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1354604238562144</v>
+        <v>-0.167215442264363</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07873606585126512</v>
+        <v>-0.06808210114600523</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2585459836624275</v>
+        <v>-0.2187703180792201</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.02893433396694354</v>
+        <v>-0.06393284911112385</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08422418412993109</v>
+        <v>0.05587101122882774</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1192002109006315</v>
+        <v>-0.1314899349506627</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.136778229664279</v>
+        <v>-0.1522158844864508</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0967858709076409</v>
+        <v>-0.1080991921647231</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.06543443903648634</v>
+        <v>-0.08992798138920428</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007089863357188233</v>
+        <v>0.02002294690799202</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.07760454555834151</v>
+        <v>-0.08287838757839507</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07428812063251559</v>
+        <v>0.05374418809642145</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1165251848312146</v>
+        <v>0.1445812405907266</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.158862651601336</v>
+        <v>-0.1803462589986181</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.280415472624286</v>
+        <v>-0.3065947494561944</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.07131799863968427</v>
+        <v>-0.07977043020615195</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1278788595294636</v>
+        <v>0.1245698010622083</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1811749628814009</v>
+        <v>-0.1913388094252928</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.007791301925744272</v>
+        <v>-0.01007444512978997</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.003277388179343945</v>
+        <v>-0.03926603821637849</v>
       </c>
     </row>
     <row r="8">
@@ -1054,79 +1059,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03033563233419542</v>
+        <v>-0.0001358103482865656</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2300070610920869</v>
+        <v>-0.2088423892759686</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02543654199304072</v>
+        <v>0.004414366045008406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04405427721174383</v>
+        <v>0.04850253546098757</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2079993296777172</v>
+        <v>-0.2368021079375125</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.07873606585126512</v>
+        <v>-0.06808210114600523</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1801060498517083</v>
+        <v>-0.125061253268812</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1602043378491308</v>
+        <v>-0.1508655951062316</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05776407877616581</v>
+        <v>0.05223707948488716</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03599021489036448</v>
+        <v>-0.03113605215718035</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01357365298140065</v>
+        <v>0.04628556985495352</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006249406145536831</v>
+        <v>0.01579433680075494</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3305841278568111</v>
+        <v>0.3366675286010631</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0138728819938388</v>
+        <v>0.01804955494089452</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1415760913109388</v>
+        <v>-0.09938867003906039</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.1995014396154836</v>
+        <v>-0.167857234856088</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1908026316173709</v>
+        <v>-0.2217478560187171</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08733721304774054</v>
+        <v>0.09039204233491172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1182429681568495</v>
+        <v>0.1218416579023868</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1465954827314442</v>
+        <v>0.1637969199169088</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1361250265757814</v>
+        <v>-0.1164543694662185</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3301374825969918</v>
+        <v>-0.2969742058455215</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1014596541156897</v>
+        <v>0.1202364640347386</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.09322834453752188</v>
+        <v>-0.06548595911697697</v>
       </c>
     </row>
     <row r="9">
@@ -1136,79 +1141,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03633878225065681</v>
+        <v>0.08430410904746641</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.03262465548527024</v>
+        <v>-0.01231536790245246</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08405945991302961</v>
+        <v>-0.03097934832898148</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3299542935597286</v>
+        <v>0.3358321108389308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01241562626470104</v>
+        <v>-0.005140770363835848</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2585459836624275</v>
+        <v>-0.2187703180792201</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1801060498517083</v>
+        <v>-0.125061253268812</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1324357872757456</v>
+        <v>-0.1371260427717139</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1134409115481081</v>
+        <v>-0.09753063720116581</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.01390836767511194</v>
+        <v>0.01168964117065046</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0439755185501574</v>
+        <v>0.01354913717359084</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1962891023535655</v>
+        <v>-0.1554429598275076</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01379917635912145</v>
+        <v>0.04447469092783533</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.05294248730464463</v>
+        <v>0.009761808199367386</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2329326496676574</v>
+        <v>0.2833846215463388</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08491204985460842</v>
+        <v>0.1176360992873489</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1762685365813332</v>
+        <v>-0.3454827324328114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1134899452236359</v>
+        <v>-0.08134590496013057</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07711273770865634</v>
+        <v>-0.04648108195955263</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02237995913864634</v>
+        <v>0.02410563206521983</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3612288288122438</v>
+        <v>-0.3023000578599637</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1770433793893441</v>
+        <v>0.2232721256069499</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.08092772077350292</v>
+        <v>-0.02942881155271856</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1026728957480521</v>
+        <v>-0.1452319412956072</v>
       </c>
     </row>
     <row r="10">
@@ -1218,79 +1223,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02022527151277422</v>
+        <v>-0.06518197803385899</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1904304170486608</v>
+        <v>0.1311458572529243</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2121035441269691</v>
+        <v>-0.2389597492136833</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1708340394968761</v>
+        <v>-0.1862569580259524</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1564434015163391</v>
+        <v>-0.1768402493286133</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.02893433396694354</v>
+        <v>-0.06393284911112385</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1602043378491308</v>
+        <v>-0.1508655951062316</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1324357872757456</v>
+        <v>-0.1371260427717139</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02168023651535294</v>
+        <v>-0.05436378339725732</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.09566207946128664</v>
+        <v>-0.1227147265602449</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0566277122463392</v>
+        <v>-0.004380557011829531</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06936437642046701</v>
+        <v>0.04960391297075023</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3300245586953593</v>
+        <v>-0.3846696432621663</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2579531825204819</v>
+        <v>-0.2493344754447739</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.01282596259336543</v>
+        <v>-0.05911577645285326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.04903694178503153</v>
+        <v>0.02661129179988407</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1985028150323692</v>
+        <v>0.2390640209713386</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002913924230924249</v>
+        <v>-0.02451339952498821</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1925492476829922</v>
+        <v>0.1650032970784867</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1640532721901378</v>
+        <v>0.1575845459196922</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00496523032544023</v>
+        <v>-0.01897746377123471</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1559352381074789</v>
+        <v>-0.2021547197389111</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1319685018923824</v>
+        <v>-0.1384426073396676</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.06116005885169464</v>
+        <v>0.085516147965012</v>
       </c>
     </row>
     <row r="11">
@@ -1300,79 +1305,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.03156057349854907</v>
+        <v>-0.05910174083749125</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02486164170619122</v>
+        <v>-0.06168451493187681</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.04308140878928639</v>
+        <v>-0.0694836871769368</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2127664205607351</v>
+        <v>0.2030837249025649</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01055909847799311</v>
+        <v>-0.02812539956889237</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08422418412993109</v>
+        <v>0.05587101122882774</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05776407877616581</v>
+        <v>0.05223707948488716</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1134409115481081</v>
+        <v>-0.09753063720116581</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.02168023651535294</v>
+        <v>-0.05436378339725732</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3997730200395039</v>
+        <v>0.3820679477550514</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.125345896648946</v>
+        <v>-0.1613680738771265</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01079724286671034</v>
+        <v>-0.02326877330680979</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08715005456427911</v>
+        <v>0.0424250029536573</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1359707559270579</v>
+        <v>-0.1397438003482599</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03024472539427947</v>
+        <v>0.00735367368939775</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0858691395808709</v>
+        <v>0.06108558869247034</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2545728293409391</v>
+        <v>0.1686632712060368</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02686430740238691</v>
+        <v>-0.01548774986786229</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3177233237716248</v>
+        <v>-0.3795390563698411</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2146340802268429</v>
+        <v>-0.244829230304824</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.33475516613236</v>
+        <v>-0.3676161765643273</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1400032459014436</v>
+        <v>0.1109830501180489</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.2510485781301872</v>
+        <v>-0.2783289338950818</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.1472711643961098</v>
+        <v>-0.03651383637248642</v>
       </c>
     </row>
     <row r="12">
@@ -1382,79 +1387,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.115036642148845</v>
+        <v>0.1108574280871432</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01908623476245801</v>
+        <v>-0.001225231000302629</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1254533554195611</v>
+        <v>0.1184643473616116</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03911441079194861</v>
+        <v>0.0291518275489075</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1053724602209355</v>
+        <v>0.06830064509733623</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1192002109006315</v>
+        <v>-0.1314899349506627</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.03599021489036448</v>
+        <v>-0.03113605215718035</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01390836767511194</v>
+        <v>0.01168964117065046</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.09566207946128664</v>
+        <v>-0.1227147265602449</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3997730200395039</v>
+        <v>0.3820679477550514</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05965251399382896</v>
+        <v>0.05390717591567577</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03434781885990516</v>
+        <v>-0.04995446107299282</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.00668494334520688</v>
+        <v>-0.03319598820854242</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2090134876274822</v>
+        <v>-0.1985904185839525</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.04090621804733596</v>
+        <v>0.03779312440710879</v>
       </c>
       <c r="R12" t="n">
-        <v>0.03488217084715253</v>
+        <v>0.0226825799563393</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1135160814253414</v>
+        <v>0.04210621173918676</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03653076945375922</v>
+        <v>0.01130983887737532</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2769041748840049</v>
+        <v>-0.3089751457432588</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2826575889425725</v>
+        <v>-0.2918048785788406</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1890970104612784</v>
+        <v>-0.1977514348219999</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.003605190983084536</v>
+        <v>-0.01316798975696106</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3659549437107336</v>
+        <v>-0.3713597415335571</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.04735420701616946</v>
+        <v>0.02938844705493248</v>
       </c>
     </row>
     <row r="13">
@@ -1464,79 +1469,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.005320585099990513</v>
+        <v>-0.01005472373352051</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.04464396500874263</v>
+        <v>-0.08554976741476467</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04508875124098461</v>
+        <v>-0.038391570805827</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03917383475926822</v>
+        <v>0.04406701542697509</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1617247728694708</v>
+        <v>-0.1771628291451114</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.136778229664279</v>
+        <v>-0.1522158844864508</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01357365298140065</v>
+        <v>0.04628556985495352</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0439755185501574</v>
+        <v>0.01354913717359084</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0566277122463392</v>
+        <v>-0.004380557011829531</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.125345896648946</v>
+        <v>-0.1613680738771265</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05965251399382896</v>
+        <v>0.05390717591567577</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.005243760980882248</v>
+        <v>-0.004102821883955172</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1197596693442678</v>
+        <v>-0.1313239820198672</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.07049946769137541</v>
+        <v>-0.01929985868684471</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1718747371566953</v>
+        <v>-0.1542383125525149</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.05916700821152293</v>
+        <v>-0.06168376615455999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07645991860444608</v>
+        <v>-0.1075879411381181</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1035799556320059</v>
+        <v>-0.101753665089694</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1183790987866176</v>
+        <v>0.111739900808406</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.08234828832571289</v>
+        <v>-0.0616911930154324</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03515964298632619</v>
+        <v>-0.02188168026367028</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.08204531409911271</v>
+        <v>-0.07438568997315603</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.1051238600483778</v>
+        <v>-0.08094752656914483</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06932040796587303</v>
+        <v>0.1456231615511814</v>
       </c>
     </row>
     <row r="14">
@@ -1546,79 +1551,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0309895504798232</v>
+        <v>-0.02919866317812313</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1559109496315521</v>
+        <v>-0.1754706779003215</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1418409488252334</v>
+        <v>-0.1397984830157049</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08402179519841492</v>
+        <v>-0.09159127843255042</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.008624186383075961</v>
+        <v>-0.04766298966051171</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0967858709076409</v>
+        <v>-0.1080991921647231</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006249406145536831</v>
+        <v>0.01579433680075494</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1962891023535655</v>
+        <v>-0.1554429598275076</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06936437642046701</v>
+        <v>0.04960391297075023</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01079724286671034</v>
+        <v>-0.02326877330680979</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.03434781885990516</v>
+        <v>-0.04995446107299282</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.005243760980882248</v>
+        <v>-0.004102821883955172</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.04745234286852737</v>
+        <v>-0.07241638380217551</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.08772254318869738</v>
+        <v>-0.07045172267503419</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.03722173527006671</v>
+        <v>-0.02849103566392459</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.215564115105108</v>
+        <v>-0.2183125001970183</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1398565870563872</v>
+        <v>-0.01902465172776079</v>
       </c>
       <c r="T14" t="n">
-        <v>0.004112589711083342</v>
+        <v>-0.01894498832772225</v>
       </c>
       <c r="U14" t="n">
-        <v>0.22664608072952</v>
+        <v>0.207904612008575</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0479832750070488</v>
+        <v>0.04421172978035786</v>
       </c>
       <c r="W14" t="n">
-        <v>0.08454677307752749</v>
+        <v>0.08111997379714103</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06794891025049291</v>
+        <v>0.06589505172888585</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02429953931932304</v>
+        <v>0.02362999287037308</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.02789058530308425</v>
+        <v>0.0528643799640067</v>
       </c>
     </row>
     <row r="15">
@@ -1628,79 +1633,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.010167815924502</v>
+        <v>-0.01652110070473159</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.09802811676286918</v>
+        <v>-0.1282986512996324</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1516497698866561</v>
+        <v>0.1494580070051232</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1413832192368523</v>
+        <v>0.1295906476988291</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1823367016379244</v>
+        <v>0.1522367335188125</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.06543443903648634</v>
+        <v>-0.08992798138920428</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3305841278568111</v>
+        <v>0.3366675286010631</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01379917635912145</v>
+        <v>0.04447469092783533</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3300245586953593</v>
+        <v>-0.3846696432621663</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08715005456427911</v>
+        <v>0.0424250029536573</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00668494334520688</v>
+        <v>-0.03319598820854242</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1197596693442678</v>
+        <v>-0.1313239820198672</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04745234286852737</v>
+        <v>-0.07241638380217551</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08933205015580693</v>
+        <v>0.1066265816431113</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.0563565803367707</v>
+        <v>-0.05138707785305217</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.3125291139021192</v>
+        <v>-0.3208846767901392</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1042601497403656</v>
+        <v>-0.21545206195815</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05092009583589224</v>
+        <v>0.02491673555036289</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01056793530875837</v>
+        <v>-0.0466679525709579</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01908468966008639</v>
+        <v>0.0148829721506038</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2307370130418688</v>
+        <v>-0.242578399860016</v>
       </c>
       <c r="X15" t="n">
-        <v>0.09069783181688047</v>
+        <v>0.08368956578710027</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.05627842158934936</v>
+        <v>0.05305054532614976</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3152947335314149</v>
+        <v>0.06942969087143219</v>
       </c>
     </row>
     <row r="16">
@@ -1710,79 +1715,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.06274862662996503</v>
+        <v>-0.01574758136923303</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.02910423308593498</v>
+        <v>0.005390803511098182</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0132706050165777</v>
+        <v>0.06099766292635559</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08743853822678514</v>
+        <v>-0.08276809575200085</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2330217345192515</v>
+        <v>0.2110941022081083</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007089863357188233</v>
+        <v>0.02002294690799202</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0138728819938388</v>
+        <v>0.01804955494089452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05294248730464463</v>
+        <v>0.009761808199367386</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2579531825204819</v>
+        <v>-0.2493344754447739</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1359707559270579</v>
+        <v>-0.1397438003482599</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2090134876274822</v>
+        <v>-0.1985904185839525</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07049946769137541</v>
+        <v>-0.01929985868684471</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.08772254318869738</v>
+        <v>-0.07045172267503419</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08933205015580693</v>
+        <v>0.1066265816431113</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1081633586227927</v>
+        <v>-0.04065846240226895</v>
       </c>
       <c r="R16" t="n">
-        <v>0.07247269255807889</v>
+        <v>0.1156587310296678</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3069515895749118</v>
+        <v>-0.3745533596754718</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2146201617295079</v>
+        <v>-0.1939733943899466</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1784421475591543</v>
+        <v>-0.1675353375639434</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1590075392541443</v>
+        <v>-0.111433446422082</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.003919722639856574</v>
+        <v>0.02707451553826761</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01870335671998494</v>
+        <v>0.06510795066722425</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.05503236046889372</v>
+        <v>0.09075713931481268</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.09513912214612021</v>
+        <v>-0.03708299663891045</v>
       </c>
     </row>
     <row r="17">
@@ -1792,79 +1797,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2879778325182079</v>
+        <v>-0.2664423905590795</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.07454092395583817</v>
+        <v>-0.09046689855553329</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1698049892625425</v>
+        <v>-0.1373443152881657</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02403164704658321</v>
+        <v>0.02757130748056327</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05473024321424005</v>
+        <v>0.04313992752110613</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.07760454555834151</v>
+        <v>-0.08287838757839507</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1415760913109388</v>
+        <v>-0.09938867003906039</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2329326496676574</v>
+        <v>0.2833846215463388</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01282596259336543</v>
+        <v>-0.05911577645285326</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03024472539427947</v>
+        <v>0.00735367368939775</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04090621804733596</v>
+        <v>0.03779312440710879</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1718747371566953</v>
+        <v>-0.1542383125525149</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03722173527006671</v>
+        <v>-0.02849103566392459</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0563565803367707</v>
+        <v>-0.05138707785305217</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1081633586227927</v>
+        <v>-0.04065846240226895</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.09842798912349347</v>
+        <v>-0.0761078875383211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.02305310578788696</v>
+        <v>-0.2524893711826397</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09519632824142604</v>
+        <v>0.1091435009796674</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09500208058369013</v>
+        <v>0.09382512925315133</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.03271090651134869</v>
+        <v>0.005307474901018358</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.06842379097350569</v>
+        <v>-0.04251446310169059</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1836433244496102</v>
+        <v>0.2064097584335682</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.04179186441927467</v>
+        <v>-0.00401956217080421</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.04767800033281317</v>
+        <v>-0.1186422786195988</v>
       </c>
     </row>
     <row r="18">
@@ -1874,79 +1879,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1005307437854741</v>
+        <v>-0.09676370678408867</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.004314750711063078</v>
+        <v>-0.009155430853510173</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3458779028144075</v>
+        <v>-0.3198448449012241</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05349517525767633</v>
+        <v>0.05056421195681789</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06478772439648009</v>
+        <v>0.05611819213621655</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07428812063251559</v>
+        <v>0.05374418809642145</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1995014396154836</v>
+        <v>-0.167857234856088</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08491204985460842</v>
+        <v>0.1176360992873489</v>
       </c>
       <c r="J18" t="n">
-        <v>0.04903694178503153</v>
+        <v>0.02661129179988407</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0858691395808709</v>
+        <v>0.06108558869247034</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03488217084715253</v>
+        <v>0.0226825799563393</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.05916700821152293</v>
+        <v>-0.06168376615455999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.215564115105108</v>
+        <v>-0.2183125001970183</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3125291139021192</v>
+        <v>-0.3208846767901392</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07247269255807889</v>
+        <v>0.1156587310296678</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.09842798912349347</v>
+        <v>-0.0761078875383211</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0394991565423679</v>
+        <v>-0.06470025130830707</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1067483064147744</v>
+        <v>-0.103780735735852</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1132795175503175</v>
+        <v>-0.1268220694961323</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1674827687580254</v>
+        <v>0.1898077207304055</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.06232924943459151</v>
+        <v>-0.05355183618835638</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1457585184034136</v>
+        <v>-0.1335124057362253</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.1267755068984762</v>
+        <v>-0.100181485395448</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.09677207839558442</v>
+        <v>-0.1368032578727822</v>
       </c>
     </row>
     <row r="19">
@@ -1956,79 +1961,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0234246176892712</v>
+        <v>-0.01344808262040014</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2537531499669427</v>
+        <v>0.09460719304213316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003225457788512108</v>
+        <v>-0.0322294158618792</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1117365121049816</v>
+        <v>-0.1499544726593419</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2920659258482997</v>
+        <v>0.07877893377184686</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1165251848312146</v>
+        <v>0.1445812405907266</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1908026316173709</v>
+        <v>-0.2217478560187171</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1762685365813332</v>
+        <v>-0.3454827324328114</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1985028150323692</v>
+        <v>0.2390640209713386</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2545728293409391</v>
+        <v>0.1686632712060368</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1135160814253414</v>
+        <v>0.04210621173918676</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07645991860444608</v>
+        <v>-0.1075879411381181</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1398565870563872</v>
+        <v>-0.01902465172776079</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1042601497403656</v>
+        <v>-0.21545206195815</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3069515895749118</v>
+        <v>-0.3745533596754718</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.02305310578788696</v>
+        <v>-0.2524893711826397</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0394991565423679</v>
+        <v>-0.06470025130830707</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2663271516029999</v>
+        <v>0.03280023732073464</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1085449571917297</v>
+        <v>-0.02166947475011432</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2244134418686628</v>
+        <v>-0.1985818342719534</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0731969511044448</v>
+        <v>0.03210825928236674</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.08395387750674896</v>
+        <v>-0.2205265430283081</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01810445295987602</v>
+        <v>-0.08264568732088431</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.001284663210330499</v>
+        <v>0.1494674775512268</v>
       </c>
     </row>
     <row r="20">
@@ -2038,79 +2043,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.289937324764146</v>
+        <v>-0.2891011301594047</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.09281486384247901</v>
+        <v>-0.1086641601778888</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09230591122672942</v>
+        <v>0.09904536120018702</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1796645355347489</v>
+        <v>0.1654187283937949</v>
       </c>
       <c r="F20" t="n">
-        <v>0.229016999092037</v>
+        <v>0.1932548170751102</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.158862651601336</v>
+        <v>-0.1803462589986181</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08733721304774054</v>
+        <v>0.09039204233491172</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1134899452236359</v>
+        <v>-0.08134590496013057</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002913924230924249</v>
+        <v>-0.02451339952498821</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02686430740238691</v>
+        <v>-0.01548774986786229</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03653076945375922</v>
+        <v>0.01130983887737532</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1035799556320059</v>
+        <v>-0.101753665089694</v>
       </c>
       <c r="N20" t="n">
-        <v>0.004112589711083342</v>
+        <v>-0.01894498832772225</v>
       </c>
       <c r="O20" t="n">
-        <v>0.05092009583589224</v>
+        <v>0.02491673555036289</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2146201617295079</v>
+        <v>-0.1939733943899466</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09519632824142604</v>
+        <v>0.1091435009796674</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.1067483064147744</v>
+        <v>-0.103780735735852</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2663271516029999</v>
+        <v>0.03280023732073464</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2194933812800505</v>
+        <v>0.1922140500735156</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1104499314444678</v>
+        <v>0.1103031632919936</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.05534942510834506</v>
+        <v>-0.06332939814824216</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.01815029925713942</v>
+        <v>-0.01794472650453139</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1143175850866475</v>
+        <v>-0.116449272685889</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.03606583401485487</v>
+        <v>-0.2284806774542587</v>
       </c>
     </row>
     <row r="21">
@@ -2120,79 +2125,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.129467551742682</v>
+        <v>-0.1389372538354036</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.05628711763244174</v>
+        <v>-0.08680389514627654</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1371483270164527</v>
+        <v>-0.1453779068901319</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1279556361747688</v>
+        <v>-0.1432502264771037</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.04960427331085888</v>
+        <v>-0.09703677862553618</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.280415472624286</v>
+        <v>-0.3065947494561944</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1182429681568495</v>
+        <v>0.1218416579023868</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07711273770865634</v>
+        <v>-0.04648108195955263</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1925492476829922</v>
+        <v>0.1650032970784867</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3177233237716248</v>
+        <v>-0.3795390563698411</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2769041748840049</v>
+        <v>-0.3089751457432588</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1183790987866176</v>
+        <v>0.111739900808406</v>
       </c>
       <c r="N21" t="n">
-        <v>0.22664608072952</v>
+        <v>0.207904612008575</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.01056793530875837</v>
+        <v>-0.0466679525709579</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1784421475591543</v>
+        <v>-0.1675353375639434</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.09500208058369013</v>
+        <v>0.09382512925315133</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.1132795175503175</v>
+        <v>-0.1268220694961323</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1085449571917297</v>
+        <v>-0.02166947475011432</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2194933812800505</v>
+        <v>0.1922140500735156</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3144954892603982</v>
+        <v>0.3042903770914575</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1415941257532347</v>
+        <v>0.1307652014861562</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1895321978418488</v>
+        <v>-0.2035829785753927</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06990410590935855</v>
+        <v>0.06114890740788414</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.1892047486147649</v>
+        <v>0.04315976044746364</v>
       </c>
     </row>
     <row r="22">
@@ -2202,79 +2207,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1274996302614811</v>
+        <v>-0.1058206984785341</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.132083829042015</v>
+        <v>-0.124628603062419</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3128475457854189</v>
+        <v>-0.2793977700291272</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1331544537086789</v>
+        <v>-0.1346600688148256</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08707703895241654</v>
+        <v>-0.1093541868981749</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07131799863968427</v>
+        <v>-0.07977043020615195</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1465954827314442</v>
+        <v>0.1637969199169088</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.02237995913864634</v>
+        <v>0.02410563206521983</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1640532721901378</v>
+        <v>0.1575845459196922</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2146340802268429</v>
+        <v>-0.244829230304824</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2826575889425725</v>
+        <v>-0.2918048785788406</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.08234828832571289</v>
+        <v>-0.0616911930154324</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0479832750070488</v>
+        <v>0.04421172978035786</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01908468966008639</v>
+        <v>0.0148829721506038</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1590075392541443</v>
+        <v>-0.111433446422082</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.03271090651134869</v>
+        <v>0.005307474901018358</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1674827687580254</v>
+        <v>0.1898077207304055</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2244134418686628</v>
+        <v>-0.1985818342719534</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1104499314444678</v>
+        <v>0.1103031632919936</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3144954892603982</v>
+        <v>0.3042903770914575</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1372081493415589</v>
+        <v>-0.1229742247387783</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1742320597743291</v>
+        <v>-0.1487229758472195</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.1804950662155986</v>
+        <v>-0.1558140028110731</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.1588837208249455</v>
+        <v>0.0430641185255701</v>
       </c>
     </row>
     <row r="23">
@@ -2284,79 +2289,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1266513046877031</v>
+        <v>-0.113435125818089</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.06565800076881249</v>
+        <v>-0.07563312811489989</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1378498937458855</v>
+        <v>0.1500949403203038</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3578306650804607</v>
+        <v>-0.3612821256797281</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.007962815931592107</v>
+        <v>-0.03863046187765157</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1278788595294636</v>
+        <v>0.1245698010622083</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1361250265757814</v>
+        <v>-0.1164543694662185</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3612288288122438</v>
+        <v>-0.3023000578599637</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00496523032544023</v>
+        <v>-0.01897746377123471</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.33475516613236</v>
+        <v>-0.3676161765643273</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1890970104612784</v>
+        <v>-0.1977514348219999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.03515964298632619</v>
+        <v>-0.02188168026367028</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08454677307752749</v>
+        <v>0.08111997379714103</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2307370130418688</v>
+        <v>-0.242578399860016</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.003919722639856574</v>
+        <v>0.02707451553826761</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.06842379097350569</v>
+        <v>-0.04251446310169059</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.06232924943459151</v>
+        <v>-0.05355183618835638</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0731969511044448</v>
+        <v>0.03210825928236674</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.05534942510834506</v>
+        <v>-0.06332939814824216</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1415941257532347</v>
+        <v>0.1307652014861562</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1372081493415589</v>
+        <v>-0.1229742247387783</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1700067314168158</v>
+        <v>-0.1543861569805574</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.5428583528980316</v>
+        <v>0.548521196928306</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1241568972719883</v>
+        <v>-0.07522216537090175</v>
       </c>
     </row>
     <row r="24">
@@ -2366,79 +2371,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.05038743634038696</v>
+        <v>-0.04131472822192009</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07812496384373757</v>
+        <v>-0.09856726194527057</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08846006394704242</v>
+        <v>0.1031424048696561</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06291715035495396</v>
+        <v>0.06156912859658701</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09823339310329221</v>
+        <v>0.07997241276484114</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1811749628814009</v>
+        <v>-0.1913388094252928</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3301374825969918</v>
+        <v>-0.2969742058455215</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1770433793893441</v>
+        <v>0.2232721256069499</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1559352381074789</v>
+        <v>-0.2021547197389111</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1400032459014436</v>
+        <v>0.1109830501180489</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.003605190983084536</v>
+        <v>-0.01316798975696106</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.08204531409911271</v>
+        <v>-0.07438568997315603</v>
       </c>
       <c r="N24" t="n">
-        <v>0.06794891025049291</v>
+        <v>0.06589505172888585</v>
       </c>
       <c r="O24" t="n">
-        <v>0.09069783181688047</v>
+        <v>0.08368956578710027</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01870335671998494</v>
+        <v>0.06510795066722425</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1836433244496102</v>
+        <v>0.2064097584335682</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.1457585184034136</v>
+        <v>-0.1335124057362253</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.08395387750674896</v>
+        <v>-0.2205265430283081</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.01815029925713942</v>
+        <v>-0.01794472650453139</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1895321978418488</v>
+        <v>-0.2035829785753927</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1742320597743291</v>
+        <v>-0.1487229758472195</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1700067314168158</v>
+        <v>-0.1543861569805574</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.01800673143806142</v>
+        <v>0.004738488957780256</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.06573628620692715</v>
+        <v>-0.02583180337029171</v>
       </c>
     </row>
     <row r="25">
@@ -2448,79 +2453,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2563450530171666</v>
+        <v>-0.2314271358869424</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1633930710272654</v>
+        <v>-0.1535980470188925</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1558624613615861</v>
+        <v>0.1784076397552233</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1064287269247117</v>
+        <v>-0.1066983155019261</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.04878234568183844</v>
+        <v>-0.07470765839608567</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.007791301925744272</v>
+        <v>-0.01007444512978997</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1014596541156897</v>
+        <v>0.1202364640347386</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08092772077350292</v>
+        <v>-0.02942881155271856</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1319685018923824</v>
+        <v>-0.1384426073396676</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2510485781301872</v>
+        <v>-0.2783289338950818</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3659549437107336</v>
+        <v>-0.3713597415335571</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1051238600483778</v>
+        <v>-0.08094752656914483</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02429953931932304</v>
+        <v>0.02362999287037308</v>
       </c>
       <c r="O25" t="n">
-        <v>0.05627842158934936</v>
+        <v>0.05305054532614976</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05503236046889372</v>
+        <v>0.09075713931481268</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.04179186441927467</v>
+        <v>-0.00401956217080421</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.1267755068984762</v>
+        <v>-0.100181485395448</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.01810445295987602</v>
+        <v>-0.08264568732088431</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1143175850866475</v>
+        <v>-0.116449272685889</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06990410590935855</v>
+        <v>0.06114890740788414</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1804950662155986</v>
+        <v>-0.1558140028110731</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5428583528980316</v>
+        <v>0.548521196928306</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.01800673143806142</v>
+        <v>0.004738488957780256</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.06072188140509899</v>
+        <v>-0.1514239703245932</v>
       </c>
     </row>
     <row r="26">
@@ -2530,76 +2535,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0606583256478611</v>
+        <v>-0.1045080928838213</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.07889468769940283</v>
+        <v>-0.1687688053973208</v>
       </c>
       <c r="D26" t="n">
-        <v>0.05260816573364549</v>
+        <v>-0.1216951930520787</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1141399123091065</v>
+        <v>0.004023742310054235</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.07569129305361902</v>
+        <v>0.004721469054563258</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.003277388179343945</v>
+        <v>-0.03926603821637849</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.09322834453752188</v>
+        <v>-0.06548595911697697</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1026728957480521</v>
+        <v>-0.1452319412956072</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06116005885169464</v>
+        <v>0.085516147965012</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1472711643961098</v>
+        <v>-0.03651383637248642</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.04735420701616946</v>
+        <v>0.02938844705493248</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06932040796587303</v>
+        <v>0.1456231615511814</v>
       </c>
       <c r="N26" t="n">
-        <v>0.02789058530308425</v>
+        <v>0.0528643799640067</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3152947335314149</v>
+        <v>0.06942969087143219</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.09513912214612021</v>
+        <v>-0.03708299663891045</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.04767800033281317</v>
+        <v>-0.1186422786195988</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.09677207839558442</v>
+        <v>-0.1368032578727822</v>
       </c>
       <c r="S26" t="n">
-        <v>0.001284663210330499</v>
+        <v>0.1494674775512268</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.03606583401485487</v>
+        <v>-0.2284806774542587</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1892047486147649</v>
+        <v>0.04315976044746364</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1588837208249455</v>
+        <v>0.0430641185255701</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1241568972719883</v>
+        <v>-0.07522216537090175</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.06573628620692715</v>
+        <v>-0.02583180337029171</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.06072188140509899</v>
+        <v>-0.1514239703245932</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
